--- a/SGI_Sistema-de-gestao-integrado/SGI_Sistema-de-gestao-da-qualidade/Registos_SGQ_Plasticom/SGQ-06_Planeamento_Alteracoes.xlsx
+++ b/SGI_Sistema-de-gestao-integrado/SGI_Sistema-de-gestao-da-qualidade/Registos_SGQ_Plasticom/SGQ-06_Planeamento_Alteracoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project Portfolios\manufacturing-performance-analytics\SGI_Sistema-de-gestao-integrado\SGI_Sistema-de-gestao-da-qualidade\Registos_SGQ_Plasticom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04D3170-4C8C-4DB7-9E9E-E9422D1E80FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD14CCC-403B-438F-BA2E-7A9DF6E1353D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -973,7 +973,7 @@
     <t>MOC-Q-26-03</t>
   </si>
   <si>
-    <t>Instalação das injetoras IM-007 e IM-008 (potes PT e tampas TE/TP/TA)</t>
+    <t>Instalação das injetoras IM-007, IM-008 e IM-009 (potes PT, tampas TE/TP; IM-009 dedicada às tampas alimentares TA)</t>
   </si>
   <si>
     <t>Capacidade para potes e tampas farma/alimentar; risco de defeitos no arranque</t>
